--- a/feedback_forms/001_peer_to_peer_relationship_survey--feedback_forms.xlsx
+++ b/feedback_forms/001_peer_to_peer_relationship_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'almost_every_day'}</t>
+          <t>almost_every_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Almost Every Day'}</t>
+          <t>Almost Every Day</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'a_few_times_a_week'}</t>
+          <t>a_few_times_a_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'A Few Times a Week'}</t>
+          <t>A Few Times a Week</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'less_than_once_a_week'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Less than Once a Week'}</t>
+          <t>Less than Once a Week</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'trustworthy'}</t>
+          <t>trustworthy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Trustworthy'}</t>
+          <t>Trustworthy</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'untrustworthy'}</t>
+          <t>untrustworthy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Untrustworthy'}</t>
+          <t>Untrustworthy</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'somewhat_trustworthy'}</t>
+          <t>somewhat_trustworthy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Somewhat Trustworthy'}</t>
+          <t>Somewhat Trustworthy</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'somewhat_untrustworthy'}</t>
+          <t>somewhat_untrustworthy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Somewhat Untrustworthy'}</t>
+          <t>Somewhat Untrustworthy</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'strongly_positive'}</t>
+          <t>strongly_positive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Strongly Positive'}</t>
+          <t>Strongly Positive</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'somewhat_positive'}</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Somewhat Positive'}</t>
+          <t>Somewhat Positive</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
